--- a/data/degradationdata.xlsx
+++ b/data/degradationdata.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="64">
   <si>
     <t>Material_Type</t>
   </si>
@@ -61,10 +61,10 @@
     <t>Cellulose Acetate</t>
   </si>
   <si>
-    <t xml:space="preserve"> Ocean Water</t>
+    <t>Ocean Water</t>
   </si>
   <si>
-    <t xml:space="preserve"> Lake Water</t>
+    <t>Lake Water</t>
   </si>
   <si>
     <t>Artificial seawater</t>
@@ -74,12 +74,6 @@
   </si>
   <si>
     <t>Tap Water</t>
-  </si>
-  <si>
-    <t>Ocean Water</t>
-  </si>
-  <si>
-    <t>Lake Water</t>
   </si>
   <si>
     <t>Sat. NaCl</t>
@@ -252,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -277,6 +271,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1905,7 +1902,7 @@
         <v>7.0</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F54" s="3">
         <v>30.0</v>
@@ -1931,7 +1928,7 @@
         <v>7.0</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F55" s="3">
         <v>90.0</v>
@@ -1957,7 +1954,7 @@
         <v>7.0</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F56" s="3">
         <v>180.0</v>
@@ -1983,7 +1980,7 @@
         <v>7.0</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F57" s="3">
         <v>270.0</v>
@@ -2009,7 +2006,7 @@
         <v>7.0</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F58" s="3">
         <v>365.0</v>
@@ -2035,7 +2032,7 @@
         <v>7.0</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F59" s="3">
         <v>30.0</v>
@@ -2061,7 +2058,7 @@
         <v>7.0</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F60" s="3">
         <v>90.0</v>
@@ -2087,7 +2084,7 @@
         <v>7.0</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F61" s="3">
         <v>180.0</v>
@@ -2113,7 +2110,7 @@
         <v>7.0</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F62" s="3">
         <v>270.0</v>
@@ -2139,7 +2136,7 @@
         <v>7.0</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F63" s="3">
         <v>365.0</v>
@@ -2425,7 +2422,7 @@
         <v>7.0</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F74" s="3">
         <v>30.0</v>
@@ -2451,7 +2448,7 @@
         <v>7.0</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F75" s="3">
         <v>90.0</v>
@@ -2477,7 +2474,7 @@
         <v>7.0</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F76" s="3">
         <v>180.0</v>
@@ -2503,7 +2500,7 @@
         <v>7.0</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F77" s="3">
         <v>270.0</v>
@@ -2529,7 +2526,7 @@
         <v>7.0</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F78" s="3">
         <v>365.0</v>
@@ -2673,7 +2670,7 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B84" s="3">
         <v>100.0</v>
@@ -2685,7 +2682,7 @@
         <v>7.0</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F84" s="3">
         <v>10.0</v>
@@ -2699,7 +2696,7 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B85" s="3">
         <v>100.0</v>
@@ -2711,7 +2708,7 @@
         <v>7.0</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F85" s="3">
         <v>22.0</v>
@@ -2725,7 +2722,7 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B86" s="3">
         <v>100.0</v>
@@ -2737,7 +2734,7 @@
         <v>7.0</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F86" s="3">
         <v>22.0</v>
@@ -2751,7 +2748,7 @@
     </row>
     <row r="87">
       <c r="A87" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B87" s="5">
         <v>100.0</v>
@@ -2763,7 +2760,7 @@
         <v>7.0</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F87" s="6">
         <v>22.0</v>
@@ -2789,7 +2786,7 @@
         <v>7.0</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F88" s="6">
         <v>14.0</v>
@@ -2815,7 +2812,7 @@
         <v>7.0</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F89" s="6">
         <v>14.0</v>
@@ -2841,7 +2838,7 @@
         <v>7.0</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F90" s="6">
         <v>14.0</v>
@@ -2867,7 +2864,7 @@
         <v>7.0</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F91" s="6">
         <v>22.0</v>
@@ -2893,7 +2890,7 @@
         <v>7.0</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F92" s="6">
         <v>27.0</v>
@@ -2919,7 +2916,7 @@
         <v>7.0</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F93" s="6">
         <v>70.0</v>
@@ -2945,7 +2942,7 @@
         <v>7.0</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F94" s="6">
         <v>28.0</v>
@@ -2959,7 +2956,7 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B95" s="3">
         <v>50.0</v>
@@ -2971,7 +2968,7 @@
         <v>7.0</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F95" s="3">
         <v>14.0</v>
@@ -2985,7 +2982,7 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B96" s="3">
         <v>50.0</v>
@@ -2997,7 +2994,7 @@
         <v>7.0</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F96" s="3">
         <v>29.0</v>
@@ -3011,7 +3008,7 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B97" s="3">
         <v>50.0</v>
@@ -3023,7 +3020,7 @@
         <v>7.0</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F97" s="3">
         <v>30.0</v>
@@ -3037,7 +3034,7 @@
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B98" s="3">
         <v>50.0</v>
@@ -3049,7 +3046,7 @@
         <v>7.0</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F98" s="3">
         <v>30.0</v>
@@ -3063,7 +3060,7 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B99" s="3">
         <v>95.0</v>
@@ -3089,7 +3086,7 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B100" s="3">
         <v>90.0</v>
@@ -3101,7 +3098,7 @@
         <v>7.5</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F100" s="3">
         <v>35.0</v>
@@ -3115,7 +3112,7 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B101" s="3">
         <v>90.0</v>
@@ -3127,7 +3124,7 @@
         <v>7.5</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F101" s="3">
         <v>35.0</v>
@@ -3141,7 +3138,7 @@
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B102" s="3">
         <v>60.0</v>
@@ -3153,7 +3150,7 @@
         <v>7.5</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F102" s="3">
         <v>30.0</v>
@@ -3167,7 +3164,7 @@
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B103" s="3">
         <v>60.0</v>
@@ -3179,7 +3176,7 @@
         <v>7.5</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F103" s="3">
         <v>30.0</v>
@@ -3193,7 +3190,7 @@
     </row>
     <row r="104">
       <c r="A104" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B104" s="5">
         <v>60.0</v>
@@ -3205,7 +3202,7 @@
         <v>8.0</v>
       </c>
       <c r="E104" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F104" s="5">
         <v>30.0</v>
@@ -3219,7 +3216,7 @@
     </row>
     <row r="105">
       <c r="A105" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B105" s="6">
         <v>92.5</v>
@@ -3231,7 +3228,7 @@
         <v>7.5</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F105" s="6">
         <v>90.0</v>
@@ -3245,7 +3242,7 @@
     </row>
     <row r="106">
       <c r="A106" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B106" s="6">
         <v>92.5</v>
@@ -3257,7 +3254,7 @@
         <v>7.0</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F106" s="6">
         <v>90.0</v>
@@ -3271,7 +3268,7 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B107" s="3">
         <v>95.0</v>
@@ -3297,7 +3294,7 @@
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B108" s="3">
         <v>95.0</v>
@@ -3323,7 +3320,7 @@
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B109" s="3">
         <v>80.0</v>
@@ -3349,7 +3346,7 @@
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B110" s="3">
         <v>45.0</v>
@@ -3375,7 +3372,7 @@
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B111" s="3">
         <v>45.0</v>
@@ -3453,7 +3450,7 @@
     </row>
     <row r="114">
       <c r="A114" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B114" s="3">
         <v>100.0</v>
@@ -3479,7 +3476,7 @@
     </row>
     <row r="115">
       <c r="A115" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B115" s="3">
         <v>100.0</v>
@@ -3505,7 +3502,7 @@
     </row>
     <row r="116">
       <c r="A116" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B116" s="3">
         <v>100.0</v>
@@ -3517,7 +3514,7 @@
         <v>7.25</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F116" s="3">
         <v>47.0</v>
@@ -3543,7 +3540,7 @@
         <v>7.25</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F117" s="3">
         <v>24.0</v>
@@ -3569,7 +3566,7 @@
         <v>7.25</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F118" s="3">
         <v>60.0</v>
@@ -3583,7 +3580,7 @@
     </row>
     <row r="119">
       <c r="A119" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B119" s="3">
         <v>97.0</v>
@@ -3595,7 +3592,7 @@
         <v>7.25</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F119" s="3">
         <v>55.0</v>
@@ -3621,7 +3618,7 @@
         <v>7.25</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F120" s="6">
         <v>55.0</v>
@@ -3647,7 +3644,7 @@
         <v>7.25</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F121" s="6">
         <v>55.0</v>
@@ -3673,7 +3670,7 @@
         <v>7.25</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F122" s="6">
         <v>55.0</v>
@@ -3699,7 +3696,7 @@
         <v>7.25</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F123" s="6">
         <v>14.0</v>
@@ -3725,7 +3722,7 @@
         <v>7.25</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F124" s="6">
         <v>14.0</v>
@@ -3751,7 +3748,7 @@
         <v>7.25</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F125" s="6">
         <v>14.0</v>
@@ -3777,7 +3774,7 @@
         <v>7.25</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F126" s="6">
         <v>30.0</v>
@@ -3803,7 +3800,7 @@
         <v>7.25</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F127" s="6">
         <v>14.0</v>
@@ -3829,7 +3826,7 @@
         <v>7.25</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F128" s="6">
         <v>14.0</v>
@@ -3855,7 +3852,7 @@
         <v>7.25</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F129" s="6">
         <v>30.0</v>
@@ -3881,7 +3878,7 @@
         <v>7.25</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F130" s="6">
         <v>30.0</v>
@@ -3895,7 +3892,7 @@
     </row>
     <row r="131">
       <c r="A131" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B131" s="6">
         <v>100.0</v>
@@ -3907,7 +3904,7 @@
         <v>7.25</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F131" s="6">
         <v>28.0</v>
@@ -3921,7 +3918,7 @@
     </row>
     <row r="132">
       <c r="A132" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B132" s="6">
         <v>100.0</v>
@@ -3933,7 +3930,7 @@
         <v>7.25</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F132" s="6">
         <v>14.0</v>
@@ -3959,7 +3956,7 @@
         <v>7.25</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F133" s="6">
         <v>84.0</v>
@@ -3973,7 +3970,7 @@
     </row>
     <row r="134">
       <c r="A134" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B134" s="6">
         <v>95.0</v>
@@ -3985,7 +3982,7 @@
         <v>7.25</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F134" s="6">
         <v>42.0</v>
@@ -3999,7 +3996,7 @@
     </row>
     <row r="135">
       <c r="A135" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B135" s="3">
         <v>95.0</v>
@@ -4011,7 +4008,7 @@
         <v>7.25</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F135" s="3">
         <v>42.0</v>
@@ -4025,7 +4022,7 @@
     </row>
     <row r="136">
       <c r="A136" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B136" s="3">
         <v>100.0</v>
@@ -4037,7 +4034,7 @@
         <v>7.25</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F136" s="3">
         <v>28.0</v>
@@ -4051,7 +4048,7 @@
     </row>
     <row r="137">
       <c r="A137" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B137" s="3">
         <v>30.0</v>
@@ -4063,7 +4060,7 @@
         <v>7.25</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F137" s="3">
         <v>84.0</v>
@@ -4077,7 +4074,7 @@
     </row>
     <row r="138">
       <c r="A138" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B138" s="3">
         <v>35.0</v>
@@ -4089,7 +4086,7 @@
         <v>7.25</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F138" s="3">
         <v>84.0</v>
@@ -4103,7 +4100,7 @@
     </row>
     <row r="139">
       <c r="A139" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B139" s="3">
         <v>95.0</v>
@@ -4115,7 +4112,7 @@
         <v>7.25</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F139" s="3">
         <v>65.0</v>
@@ -4129,7 +4126,7 @@
     </row>
     <row r="140">
       <c r="A140" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B140" s="3">
         <v>100.0</v>
@@ -4141,7 +4138,7 @@
         <v>7.0</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F140" s="3">
         <v>28.0</v>
@@ -4155,7 +4152,7 @@
     </row>
     <row r="141">
       <c r="A141" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B141" s="3">
         <v>95.0</v>
@@ -4167,7 +4164,7 @@
         <v>7.0</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F141" s="3">
         <v>14.0</v>
@@ -4181,7 +4178,7 @@
     </row>
     <row r="142">
       <c r="A142" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B142" s="3">
         <v>95.0</v>
@@ -4193,7 +4190,7 @@
         <v>7.0</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F142" s="3">
         <v>56.0</v>
@@ -4207,7 +4204,7 @@
     </row>
     <row r="143">
       <c r="A143" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B143" s="3">
         <v>100.0</v>
@@ -4219,7 +4216,7 @@
         <v>7.0</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F143" s="3">
         <v>28.0</v>
@@ -4233,7 +4230,7 @@
     </row>
     <row r="144">
       <c r="A144" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B144" s="3">
         <v>100.0</v>
@@ -4245,7 +4242,7 @@
         <v>7.0</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F144" s="3">
         <v>42.0</v>
@@ -4259,7 +4256,7 @@
     </row>
     <row r="145">
       <c r="A145" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B145" s="6">
         <v>95.0</v>
@@ -4271,7 +4268,7 @@
         <v>7.0</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F145" s="5">
         <v>28.0</v>
@@ -4298,7 +4295,7 @@
         <v>7.0</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F146" s="6">
         <v>84.0</v>
@@ -4313,7 +4310,7 @@
     </row>
     <row r="147">
       <c r="A147" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B147" s="6">
         <v>95.0</v>
@@ -4325,7 +4322,7 @@
         <v>7.0</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F147" s="6">
         <v>84.0</v>
@@ -4339,7 +4336,7 @@
     </row>
     <row r="148">
       <c r="A148" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B148" s="6">
         <v>95.0</v>
@@ -4351,7 +4348,7 @@
         <v>7.0</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F148" s="6">
         <v>84.0</v>
@@ -4365,7 +4362,7 @@
     </row>
     <row r="149">
       <c r="A149" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B149" s="6">
         <v>70.0</v>
@@ -4377,7 +4374,7 @@
         <v>7.0</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F149" s="6">
         <v>84.0</v>
@@ -4391,7 +4388,7 @@
     </row>
     <row r="150">
       <c r="A150" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B150" s="6">
         <v>95.0</v>
@@ -4403,7 +4400,7 @@
         <v>7.0</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F150" s="6">
         <v>200.0</v>
@@ -4417,7 +4414,7 @@
     </row>
     <row r="151">
       <c r="A151" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B151" s="6">
         <v>95.0</v>
@@ -4429,7 +4426,7 @@
         <v>7.0</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F151" s="6">
         <v>46.0</v>
@@ -4443,7 +4440,7 @@
     </row>
     <row r="152">
       <c r="A152" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B152" s="6">
         <v>95.0</v>
@@ -4455,7 +4452,7 @@
         <v>7.0</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F152" s="6">
         <v>46.0</v>
@@ -4469,7 +4466,7 @@
     </row>
     <row r="153">
       <c r="A153" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B153" s="6">
         <v>100.0</v>
@@ -4481,7 +4478,7 @@
         <v>7.0</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F153" s="6">
         <v>157.0</v>
@@ -4495,7 +4492,7 @@
     </row>
     <row r="154">
       <c r="A154" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B154" s="6">
         <v>95.0</v>
@@ -4507,7 +4504,7 @@
         <v>7.0</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F154" s="6">
         <v>157.0</v>
@@ -4521,7 +4518,7 @@
     </row>
     <row r="155">
       <c r="A155" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B155" s="6">
         <v>100.0</v>
@@ -4547,7 +4544,7 @@
     </row>
     <row r="156">
       <c r="A156" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B156" s="6">
         <v>95.0</v>
@@ -4569,6 +4566,4062 @@
       </c>
       <c r="H156" s="6">
         <v>2.5</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B157" s="9">
+        <v>78.0</v>
+      </c>
+      <c r="C157" s="9">
+        <v>20.0</v>
+      </c>
+      <c r="D157" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="E157" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F157" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="G157" s="9">
+        <v>92.0</v>
+      </c>
+      <c r="H157" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B158" s="9">
+        <v>80.0</v>
+      </c>
+      <c r="C158" s="9">
+        <v>20.0</v>
+      </c>
+      <c r="D158" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E158" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F158" s="9">
+        <v>14.0</v>
+      </c>
+      <c r="G158" s="9">
+        <v>78.0</v>
+      </c>
+      <c r="H158" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B159" s="9">
+        <v>82.0</v>
+      </c>
+      <c r="C159" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="D159" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E159" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F159" s="9">
+        <v>21.0</v>
+      </c>
+      <c r="G159" s="9">
+        <v>52.0</v>
+      </c>
+      <c r="H159" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B160" s="9">
+        <v>75.0</v>
+      </c>
+      <c r="C160" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="D160" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="E160" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F160" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="G160" s="9">
+        <v>35.0</v>
+      </c>
+      <c r="H160" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B161" s="9">
+        <v>83.0</v>
+      </c>
+      <c r="C161" s="9">
+        <v>22.0</v>
+      </c>
+      <c r="D161" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E161" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F161" s="9">
+        <v>45.0</v>
+      </c>
+      <c r="G161" s="9">
+        <v>31.0</v>
+      </c>
+      <c r="H161" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B162" s="9">
+        <v>80.0</v>
+      </c>
+      <c r="C162" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="D162" s="9">
+        <v>7.1</v>
+      </c>
+      <c r="E162" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F162" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="G162" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="H162" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B163" s="9">
+        <v>77.0</v>
+      </c>
+      <c r="C163" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="D163" s="9">
+        <v>6.9</v>
+      </c>
+      <c r="E163" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F163" s="9">
+        <v>75.0</v>
+      </c>
+      <c r="G163" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="H163" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B164" s="9">
+        <v>81.0</v>
+      </c>
+      <c r="C164" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="D164" s="9">
+        <v>7.3</v>
+      </c>
+      <c r="E164" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F164" s="9">
+        <v>90.0</v>
+      </c>
+      <c r="G164" s="9">
+        <v>32.0</v>
+      </c>
+      <c r="H164" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B165" s="9">
+        <v>65.0</v>
+      </c>
+      <c r="C165" s="9">
+        <v>20.0</v>
+      </c>
+      <c r="D165" s="9">
+        <v>6.6</v>
+      </c>
+      <c r="E165" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F165" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="G165" s="9">
+        <v>88.0</v>
+      </c>
+      <c r="H165" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B166" s="9">
+        <v>70.0</v>
+      </c>
+      <c r="C166" s="9">
+        <v>22.0</v>
+      </c>
+      <c r="D166" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E166" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F166" s="9">
+        <v>14.0</v>
+      </c>
+      <c r="G166" s="9">
+        <v>75.0</v>
+      </c>
+      <c r="H166" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B167" s="9">
+        <v>68.0</v>
+      </c>
+      <c r="C167" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="D167" s="9">
+        <v>7.4</v>
+      </c>
+      <c r="E167" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F167" s="9">
+        <v>21.0</v>
+      </c>
+      <c r="G167" s="9">
+        <v>58.0</v>
+      </c>
+      <c r="H167" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B168" s="9">
+        <v>72.0</v>
+      </c>
+      <c r="C168" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="D168" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E168" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F168" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="G168" s="9">
+        <v>48.0</v>
+      </c>
+      <c r="H168" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B169" s="9">
+        <v>61.0</v>
+      </c>
+      <c r="C169" s="9">
+        <v>24.0</v>
+      </c>
+      <c r="D169" s="9">
+        <v>6.7</v>
+      </c>
+      <c r="E169" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F169" s="9">
+        <v>40.0</v>
+      </c>
+      <c r="G169" s="9">
+        <v>42.0</v>
+      </c>
+      <c r="H169" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B170" s="9">
+        <v>75.0</v>
+      </c>
+      <c r="C170" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="D170" s="9">
+        <v>7.1</v>
+      </c>
+      <c r="E170" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F170" s="9">
+        <v>50.0</v>
+      </c>
+      <c r="G170" s="9">
+        <v>41.0</v>
+      </c>
+      <c r="H170" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B171" s="9">
+        <v>67.0</v>
+      </c>
+      <c r="C171" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="D171" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E171" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F171" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="G171" s="9">
+        <v>42.0</v>
+      </c>
+      <c r="H171" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B172" s="9">
+        <v>72.0</v>
+      </c>
+      <c r="C172" s="9">
+        <v>20.0</v>
+      </c>
+      <c r="D172" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="E172" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F172" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="G172" s="9">
+        <v>89.0</v>
+      </c>
+      <c r="H172" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B173" s="9">
+        <v>78.0</v>
+      </c>
+      <c r="C173" s="9">
+        <v>22.0</v>
+      </c>
+      <c r="D173" s="9">
+        <v>6.9</v>
+      </c>
+      <c r="E173" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F173" s="9">
+        <v>14.0</v>
+      </c>
+      <c r="G173" s="9">
+        <v>74.0</v>
+      </c>
+      <c r="H173" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B174" s="9">
+        <v>75.0</v>
+      </c>
+      <c r="C174" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="D174" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E174" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F174" s="9">
+        <v>21.0</v>
+      </c>
+      <c r="G174" s="9">
+        <v>65.0</v>
+      </c>
+      <c r="H174" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B175" s="9">
+        <v>68.0</v>
+      </c>
+      <c r="C175" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="D175" s="9">
+        <v>7.3</v>
+      </c>
+      <c r="E175" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F175" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="G175" s="9">
+        <v>45.0</v>
+      </c>
+      <c r="H175" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B176" s="9">
+        <v>80.0</v>
+      </c>
+      <c r="C176" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="D176" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E176" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F176" s="9">
+        <v>45.0</v>
+      </c>
+      <c r="G176" s="9">
+        <v>38.0</v>
+      </c>
+      <c r="H176" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B177" s="9">
+        <v>65.0</v>
+      </c>
+      <c r="C177" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="D177" s="9">
+        <v>7.1</v>
+      </c>
+      <c r="E177" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F177" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="G177" s="9">
+        <v>29.0</v>
+      </c>
+      <c r="H177" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B178" s="9">
+        <v>76.0</v>
+      </c>
+      <c r="C178" s="9">
+        <v>24.0</v>
+      </c>
+      <c r="D178" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E178" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F178" s="9">
+        <v>90.0</v>
+      </c>
+      <c r="G178" s="9">
+        <v>27.0</v>
+      </c>
+      <c r="H178" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B179" s="9">
+        <v>73.0</v>
+      </c>
+      <c r="C179" s="9">
+        <v>27.0</v>
+      </c>
+      <c r="D179" s="9">
+        <v>6.7</v>
+      </c>
+      <c r="E179" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F179" s="9">
+        <v>120.0</v>
+      </c>
+      <c r="G179" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="H179" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B180" s="9">
+        <v>98.0</v>
+      </c>
+      <c r="C180" s="9">
+        <v>20.0</v>
+      </c>
+      <c r="D180" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="E180" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F180" s="9">
+        <v>5.0</v>
+      </c>
+      <c r="G180" s="9">
+        <v>85.0</v>
+      </c>
+      <c r="H180" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B181" s="9">
+        <v>96.0</v>
+      </c>
+      <c r="C181" s="9">
+        <v>22.0</v>
+      </c>
+      <c r="D181" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F181" s="9">
+        <v>10.0</v>
+      </c>
+      <c r="G181" s="9">
+        <v>65.0</v>
+      </c>
+      <c r="H181" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B182" s="9">
+        <v>97.0</v>
+      </c>
+      <c r="C182" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="D182" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E182" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F182" s="9">
+        <v>15.0</v>
+      </c>
+      <c r="G182" s="9">
+        <v>55.0</v>
+      </c>
+      <c r="H182" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B183" s="9">
+        <v>99.0</v>
+      </c>
+      <c r="C183" s="9">
+        <v>27.0</v>
+      </c>
+      <c r="D183" s="9">
+        <v>7.1</v>
+      </c>
+      <c r="E183" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F183" s="9">
+        <v>20.0</v>
+      </c>
+      <c r="G183" s="9">
+        <v>45.0</v>
+      </c>
+      <c r="H183" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B184" s="9">
+        <v>95.0</v>
+      </c>
+      <c r="C184" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="D184" s="9">
+        <v>7.4</v>
+      </c>
+      <c r="E184" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F184" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="G184" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="H184" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B185" s="9">
+        <v>98.0</v>
+      </c>
+      <c r="C185" s="9">
+        <v>23.0</v>
+      </c>
+      <c r="D185" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E185" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F185" s="9">
+        <v>45.0</v>
+      </c>
+      <c r="G185" s="9">
+        <v>18.0</v>
+      </c>
+      <c r="H185" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B186" s="9">
+        <v>96.0</v>
+      </c>
+      <c r="C186" s="9">
+        <v>35.0</v>
+      </c>
+      <c r="D186" s="9">
+        <v>7.3</v>
+      </c>
+      <c r="E186" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F186" s="9">
+        <v>50.0</v>
+      </c>
+      <c r="G186" s="9">
+        <v>18.0</v>
+      </c>
+      <c r="H186" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B187" s="9">
+        <v>97.0</v>
+      </c>
+      <c r="C187" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="D187" s="9">
+        <v>6.9</v>
+      </c>
+      <c r="E187" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F187" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="G187" s="9">
+        <v>14.0</v>
+      </c>
+      <c r="H187" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B188" s="9">
+        <v>5.0</v>
+      </c>
+      <c r="C188" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="D188" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E188" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F188" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="G188" s="9">
+        <v>88.0</v>
+      </c>
+      <c r="H188" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B189" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="C189" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="D189" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E189" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F189" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="G189" s="9">
+        <v>72.0</v>
+      </c>
+      <c r="H189" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B190" s="9">
+        <v>3.0</v>
+      </c>
+      <c r="C190" s="9">
+        <v>35.0</v>
+      </c>
+      <c r="D190" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E190" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F190" s="9">
+        <v>90.0</v>
+      </c>
+      <c r="G190" s="9">
+        <v>55.0</v>
+      </c>
+      <c r="H190" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B191" s="9">
+        <v>10.0</v>
+      </c>
+      <c r="C191" s="9">
+        <v>40.0</v>
+      </c>
+      <c r="D191" s="9">
+        <v>7.3</v>
+      </c>
+      <c r="E191" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F191" s="9">
+        <v>120.0</v>
+      </c>
+      <c r="G191" s="9">
+        <v>68.0</v>
+      </c>
+      <c r="H191" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B192" s="9">
+        <v>4.0</v>
+      </c>
+      <c r="C192" s="9">
+        <v>45.0</v>
+      </c>
+      <c r="D192" s="9">
+        <v>6.9</v>
+      </c>
+      <c r="E192" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F192" s="9">
+        <v>150.0</v>
+      </c>
+      <c r="G192" s="9">
+        <v>48.0</v>
+      </c>
+      <c r="H192" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B193" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="C193" s="9">
+        <v>50.0</v>
+      </c>
+      <c r="D193" s="9">
+        <v>7.1</v>
+      </c>
+      <c r="E193" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F193" s="9">
+        <v>180.0</v>
+      </c>
+      <c r="G193" s="9">
+        <v>62.0</v>
+      </c>
+      <c r="H193" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B194" s="9">
+        <v>2.0</v>
+      </c>
+      <c r="C194" s="9">
+        <v>55.0</v>
+      </c>
+      <c r="D194" s="9">
+        <v>7.4</v>
+      </c>
+      <c r="E194" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F194" s="9">
+        <v>240.0</v>
+      </c>
+      <c r="G194" s="9">
+        <v>55.0</v>
+      </c>
+      <c r="H194" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B195" s="9">
+        <v>6.0</v>
+      </c>
+      <c r="C195" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="D195" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E195" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F195" s="9">
+        <v>365.0</v>
+      </c>
+      <c r="G195" s="9">
+        <v>42.0</v>
+      </c>
+      <c r="H195" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B196" s="9">
+        <v>99.0</v>
+      </c>
+      <c r="C196" s="9">
+        <v>20.0</v>
+      </c>
+      <c r="D196" s="9">
+        <v>5.8</v>
+      </c>
+      <c r="E196" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F196" s="9">
+        <v>10.0</v>
+      </c>
+      <c r="G196" s="9">
+        <v>87.0</v>
+      </c>
+      <c r="H196" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B197" s="9">
+        <v>96.0</v>
+      </c>
+      <c r="C197" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="D197" s="9">
+        <v>6.2</v>
+      </c>
+      <c r="E197" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F197" s="9">
+        <v>20.0</v>
+      </c>
+      <c r="G197" s="9">
+        <v>72.0</v>
+      </c>
+      <c r="H197" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B198" s="9">
+        <v>98.0</v>
+      </c>
+      <c r="C198" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="D198" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E198" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F198" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="G198" s="9">
+        <v>58.0</v>
+      </c>
+      <c r="H198" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B199" s="9">
+        <v>98.0</v>
+      </c>
+      <c r="C199" s="9">
+        <v>35.0</v>
+      </c>
+      <c r="D199" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E199" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F199" s="9">
+        <v>50.0</v>
+      </c>
+      <c r="G199" s="9">
+        <v>42.0</v>
+      </c>
+      <c r="H199" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B200" s="9">
+        <v>95.0</v>
+      </c>
+      <c r="C200" s="9">
+        <v>40.0</v>
+      </c>
+      <c r="D200" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E200" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F200" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="G200" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="H200" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B201" s="9">
+        <v>97.0</v>
+      </c>
+      <c r="C201" s="9">
+        <v>45.0</v>
+      </c>
+      <c r="D201" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="E201" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F201" s="9">
+        <v>90.0</v>
+      </c>
+      <c r="G201" s="9">
+        <v>32.0</v>
+      </c>
+      <c r="H201" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B202" s="9">
+        <v>99.0</v>
+      </c>
+      <c r="C202" s="9">
+        <v>50.0</v>
+      </c>
+      <c r="D202" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="E202" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F202" s="9">
+        <v>120.0</v>
+      </c>
+      <c r="G202" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="H202" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B203" s="9">
+        <v>96.0</v>
+      </c>
+      <c r="C203" s="9">
+        <v>55.0</v>
+      </c>
+      <c r="D203" s="9">
+        <v>7.8</v>
+      </c>
+      <c r="E203" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F203" s="9">
+        <v>150.0</v>
+      </c>
+      <c r="G203" s="9">
+        <v>24.0</v>
+      </c>
+      <c r="H203" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B204" s="9">
+        <v>98.0</v>
+      </c>
+      <c r="C204" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="D204" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E204" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F204" s="9">
+        <v>180.0</v>
+      </c>
+      <c r="G204" s="9">
+        <v>21.0</v>
+      </c>
+      <c r="H204" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B205" s="9">
+        <v>44.0</v>
+      </c>
+      <c r="C205" s="9">
+        <v>20.0</v>
+      </c>
+      <c r="D205" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E205" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F205" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="G205" s="9">
+        <v>92.0</v>
+      </c>
+      <c r="H205" s="9">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B206" s="9">
+        <v>43.0</v>
+      </c>
+      <c r="C206" s="9">
+        <v>22.0</v>
+      </c>
+      <c r="D206" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E206" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F206" s="9">
+        <v>45.0</v>
+      </c>
+      <c r="G206" s="9">
+        <v>85.0</v>
+      </c>
+      <c r="H206" s="9">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B207" s="9">
+        <v>45.0</v>
+      </c>
+      <c r="C207" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="D207" s="9">
+        <v>7.1</v>
+      </c>
+      <c r="E207" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F207" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="G207" s="9">
+        <v>80.0</v>
+      </c>
+      <c r="H207" s="9">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B208" s="9">
+        <v>42.0</v>
+      </c>
+      <c r="C208" s="9">
+        <v>27.0</v>
+      </c>
+      <c r="D208" s="9">
+        <v>6.9</v>
+      </c>
+      <c r="E208" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F208" s="9">
+        <v>90.0</v>
+      </c>
+      <c r="G208" s="9">
+        <v>75.0</v>
+      </c>
+      <c r="H208" s="9">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B209" s="9">
+        <v>44.0</v>
+      </c>
+      <c r="C209" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="D209" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E209" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F209" s="9">
+        <v>120.0</v>
+      </c>
+      <c r="G209" s="9">
+        <v>72.0</v>
+      </c>
+      <c r="H209" s="9">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B210" s="9">
+        <v>43.0</v>
+      </c>
+      <c r="C210" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="D210" s="9">
+        <v>7.3</v>
+      </c>
+      <c r="E210" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F210" s="9">
+        <v>150.0</v>
+      </c>
+      <c r="G210" s="9">
+        <v>70.0</v>
+      </c>
+      <c r="H210" s="9">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B211" s="9">
+        <v>45.0</v>
+      </c>
+      <c r="C211" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="D211" s="9">
+        <v>6.7</v>
+      </c>
+      <c r="E211" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F211" s="9">
+        <v>180.0</v>
+      </c>
+      <c r="G211" s="9">
+        <v>68.0</v>
+      </c>
+      <c r="H211" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B212" s="9">
+        <v>79.0</v>
+      </c>
+      <c r="C212" s="9">
+        <v>21.0</v>
+      </c>
+      <c r="D212" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E212" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F212" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="G212" s="9">
+        <v>89.0</v>
+      </c>
+      <c r="H212" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B213" s="9">
+        <v>76.0</v>
+      </c>
+      <c r="C213" s="9">
+        <v>24.0</v>
+      </c>
+      <c r="D213" s="9">
+        <v>6.6</v>
+      </c>
+      <c r="E213" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F213" s="9">
+        <v>16.0</v>
+      </c>
+      <c r="G213" s="9">
+        <v>73.0</v>
+      </c>
+      <c r="H213" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B214" s="9">
+        <v>84.0</v>
+      </c>
+      <c r="C214" s="9">
+        <v>27.0</v>
+      </c>
+      <c r="D214" s="9">
+        <v>7.4</v>
+      </c>
+      <c r="E214" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F214" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="G214" s="9">
+        <v>48.0</v>
+      </c>
+      <c r="H214" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B215" s="9">
+        <v>81.0</v>
+      </c>
+      <c r="C215" s="9">
+        <v>29.0</v>
+      </c>
+      <c r="D215" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E215" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F215" s="9">
+        <v>35.0</v>
+      </c>
+      <c r="G215" s="9">
+        <v>38.0</v>
+      </c>
+      <c r="H215" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B216" s="9">
+        <v>69.0</v>
+      </c>
+      <c r="C216" s="9">
+        <v>21.0</v>
+      </c>
+      <c r="D216" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E216" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F216" s="9">
+        <v>9.0</v>
+      </c>
+      <c r="G216" s="9">
+        <v>87.0</v>
+      </c>
+      <c r="H216" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B217" s="9">
+        <v>64.0</v>
+      </c>
+      <c r="C217" s="9">
+        <v>23.0</v>
+      </c>
+      <c r="D217" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="E217" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F217" s="9">
+        <v>16.0</v>
+      </c>
+      <c r="G217" s="9">
+        <v>71.0</v>
+      </c>
+      <c r="H217" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B218" s="9">
+        <v>73.0</v>
+      </c>
+      <c r="C218" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="D218" s="9">
+        <v>7.1</v>
+      </c>
+      <c r="E218" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F218" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="G218" s="9">
+        <v>54.0</v>
+      </c>
+      <c r="H218" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B219" s="9">
+        <v>62.0</v>
+      </c>
+      <c r="C219" s="9">
+        <v>29.0</v>
+      </c>
+      <c r="D219" s="9">
+        <v>7.3</v>
+      </c>
+      <c r="E219" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F219" s="9">
+        <v>35.0</v>
+      </c>
+      <c r="G219" s="9">
+        <v>44.0</v>
+      </c>
+      <c r="H219" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B220" s="9">
+        <v>77.0</v>
+      </c>
+      <c r="C220" s="9">
+        <v>21.0</v>
+      </c>
+      <c r="D220" s="9">
+        <v>6.7</v>
+      </c>
+      <c r="E220" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F220" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="G220" s="9">
+        <v>88.0</v>
+      </c>
+      <c r="H220" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B221" s="9">
+        <v>71.0</v>
+      </c>
+      <c r="C221" s="9">
+        <v>23.0</v>
+      </c>
+      <c r="D221" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E221" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F221" s="9">
+        <v>16.0</v>
+      </c>
+      <c r="G221" s="9">
+        <v>71.0</v>
+      </c>
+      <c r="H221" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B222" s="9">
+        <v>79.0</v>
+      </c>
+      <c r="C222" s="9">
+        <v>27.0</v>
+      </c>
+      <c r="D222" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E222" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F222" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="G222" s="9">
+        <v>62.0</v>
+      </c>
+      <c r="H222" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B223" s="9">
+        <v>70.0</v>
+      </c>
+      <c r="C223" s="9">
+        <v>29.0</v>
+      </c>
+      <c r="D223" s="9">
+        <v>7.1</v>
+      </c>
+      <c r="E223" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F223" s="9">
+        <v>40.0</v>
+      </c>
+      <c r="G223" s="9">
+        <v>32.0</v>
+      </c>
+      <c r="H223" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B224" s="9">
+        <v>97.0</v>
+      </c>
+      <c r="C224" s="9">
+        <v>21.0</v>
+      </c>
+      <c r="D224" s="9">
+        <v>6.6</v>
+      </c>
+      <c r="E224" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F224" s="9">
+        <v>6.0</v>
+      </c>
+      <c r="G224" s="9">
+        <v>82.0</v>
+      </c>
+      <c r="H224" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B225" s="9">
+        <v>99.0</v>
+      </c>
+      <c r="C225" s="9">
+        <v>24.0</v>
+      </c>
+      <c r="D225" s="9">
+        <v>6.9</v>
+      </c>
+      <c r="E225" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F225" s="9">
+        <v>12.0</v>
+      </c>
+      <c r="G225" s="9">
+        <v>62.0</v>
+      </c>
+      <c r="H225" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B226" s="9">
+        <v>95.0</v>
+      </c>
+      <c r="C226" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="D226" s="9">
+        <v>7.3</v>
+      </c>
+      <c r="E226" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F226" s="9">
+        <v>18.0</v>
+      </c>
+      <c r="G226" s="9">
+        <v>52.0</v>
+      </c>
+      <c r="H226" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B227" s="9">
+        <v>98.0</v>
+      </c>
+      <c r="C227" s="9">
+        <v>29.0</v>
+      </c>
+      <c r="D227" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E227" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F227" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="G227" s="9">
+        <v>42.0</v>
+      </c>
+      <c r="H227" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B228" s="9">
+        <v>96.0</v>
+      </c>
+      <c r="C228" s="9">
+        <v>32.0</v>
+      </c>
+      <c r="D228" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E228" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F228" s="9">
+        <v>35.0</v>
+      </c>
+      <c r="G228" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="H228" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B229" s="9">
+        <v>9.0</v>
+      </c>
+      <c r="C229" s="9">
+        <v>27.0</v>
+      </c>
+      <c r="D229" s="9">
+        <v>6.9</v>
+      </c>
+      <c r="E229" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F229" s="9">
+        <v>35.0</v>
+      </c>
+      <c r="G229" s="9">
+        <v>82.0</v>
+      </c>
+      <c r="H229" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B230" s="9">
+        <v>6.0</v>
+      </c>
+      <c r="C230" s="9">
+        <v>32.0</v>
+      </c>
+      <c r="D230" s="9">
+        <v>7.1</v>
+      </c>
+      <c r="E230" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F230" s="9">
+        <v>70.0</v>
+      </c>
+      <c r="G230" s="9">
+        <v>68.0</v>
+      </c>
+      <c r="H230" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B231" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="C231" s="9">
+        <v>37.0</v>
+      </c>
+      <c r="D231" s="9">
+        <v>7.3</v>
+      </c>
+      <c r="E231" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F231" s="9">
+        <v>100.0</v>
+      </c>
+      <c r="G231" s="9">
+        <v>52.0</v>
+      </c>
+      <c r="H231" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B232" s="9">
+        <v>4.0</v>
+      </c>
+      <c r="C232" s="9">
+        <v>42.0</v>
+      </c>
+      <c r="D232" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E232" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F232" s="9">
+        <v>130.0</v>
+      </c>
+      <c r="G232" s="9">
+        <v>65.0</v>
+      </c>
+      <c r="H232" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B233" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="C233" s="9">
+        <v>47.0</v>
+      </c>
+      <c r="D233" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E233" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F233" s="9">
+        <v>160.0</v>
+      </c>
+      <c r="G233" s="9">
+        <v>45.0</v>
+      </c>
+      <c r="H233" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B234" s="9">
+        <v>98.0</v>
+      </c>
+      <c r="C234" s="9">
+        <v>22.0</v>
+      </c>
+      <c r="D234" s="9">
+        <v>6.0</v>
+      </c>
+      <c r="E234" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F234" s="9">
+        <v>12.0</v>
+      </c>
+      <c r="G234" s="9">
+        <v>85.0</v>
+      </c>
+      <c r="H234" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B235" s="9">
+        <v>97.0</v>
+      </c>
+      <c r="C235" s="9">
+        <v>27.0</v>
+      </c>
+      <c r="D235" s="9">
+        <v>6.4</v>
+      </c>
+      <c r="E235" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F235" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="G235" s="9">
+        <v>68.0</v>
+      </c>
+      <c r="H235" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B236" s="9">
+        <v>99.0</v>
+      </c>
+      <c r="C236" s="9">
+        <v>32.0</v>
+      </c>
+      <c r="D236" s="9">
+        <v>6.9</v>
+      </c>
+      <c r="E236" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F236" s="9">
+        <v>40.0</v>
+      </c>
+      <c r="G236" s="9">
+        <v>55.0</v>
+      </c>
+      <c r="H236" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B237" s="9">
+        <v>96.0</v>
+      </c>
+      <c r="C237" s="9">
+        <v>37.0</v>
+      </c>
+      <c r="D237" s="9">
+        <v>7.1</v>
+      </c>
+      <c r="E237" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F237" s="9">
+        <v>58.0</v>
+      </c>
+      <c r="G237" s="9">
+        <v>38.0</v>
+      </c>
+      <c r="H237" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B238" s="9">
+        <v>95.0</v>
+      </c>
+      <c r="C238" s="9">
+        <v>42.0</v>
+      </c>
+      <c r="D238" s="9">
+        <v>7.3</v>
+      </c>
+      <c r="E238" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F238" s="9">
+        <v>70.0</v>
+      </c>
+      <c r="G238" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="H238" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B239" s="9">
+        <v>97.0</v>
+      </c>
+      <c r="C239" s="9">
+        <v>48.0</v>
+      </c>
+      <c r="D239" s="9">
+        <v>7.6</v>
+      </c>
+      <c r="E239" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F239" s="9">
+        <v>100.0</v>
+      </c>
+      <c r="G239" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="H239" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B240" s="9">
+        <v>98.0</v>
+      </c>
+      <c r="C240" s="9">
+        <v>53.0</v>
+      </c>
+      <c r="D240" s="9">
+        <v>6.7</v>
+      </c>
+      <c r="E240" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F240" s="9">
+        <v>130.0</v>
+      </c>
+      <c r="G240" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="H240" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B241" s="9">
+        <v>43.0</v>
+      </c>
+      <c r="C241" s="9">
+        <v>21.0</v>
+      </c>
+      <c r="D241" s="9">
+        <v>6.9</v>
+      </c>
+      <c r="E241" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F241" s="9">
+        <v>35.0</v>
+      </c>
+      <c r="G241" s="9">
+        <v>90.0</v>
+      </c>
+      <c r="H241" s="9">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B242" s="9">
+        <v>42.0</v>
+      </c>
+      <c r="C242" s="9">
+        <v>24.0</v>
+      </c>
+      <c r="D242" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E242" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F242" s="9">
+        <v>50.0</v>
+      </c>
+      <c r="G242" s="9">
+        <v>82.0</v>
+      </c>
+      <c r="H242" s="9">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B243" s="9">
+        <v>44.0</v>
+      </c>
+      <c r="C243" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="D243" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E243" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F243" s="9">
+        <v>65.0</v>
+      </c>
+      <c r="G243" s="9">
+        <v>78.0</v>
+      </c>
+      <c r="H243" s="9">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B244" s="9">
+        <v>45.0</v>
+      </c>
+      <c r="C244" s="9">
+        <v>29.0</v>
+      </c>
+      <c r="D244" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E244" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F244" s="9">
+        <v>95.0</v>
+      </c>
+      <c r="G244" s="9">
+        <v>73.0</v>
+      </c>
+      <c r="H244" s="9">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B245" s="9">
+        <v>82.0</v>
+      </c>
+      <c r="C245" s="9">
+        <v>23.0</v>
+      </c>
+      <c r="D245" s="9">
+        <v>6.7</v>
+      </c>
+      <c r="E245" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F245" s="9">
+        <v>10.0</v>
+      </c>
+      <c r="G245" s="9">
+        <v>86.0</v>
+      </c>
+      <c r="H245" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B246" s="9">
+        <v>77.0</v>
+      </c>
+      <c r="C246" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="D246" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E246" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F246" s="9">
+        <v>18.0</v>
+      </c>
+      <c r="G246" s="9">
+        <v>70.0</v>
+      </c>
+      <c r="H246" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B247" s="9">
+        <v>66.0</v>
+      </c>
+      <c r="C247" s="9">
+        <v>22.0</v>
+      </c>
+      <c r="D247" s="9">
+        <v>6.9</v>
+      </c>
+      <c r="E247" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F247" s="9">
+        <v>10.0</v>
+      </c>
+      <c r="G247" s="9">
+        <v>85.0</v>
+      </c>
+      <c r="H247" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B248" s="9">
+        <v>71.0</v>
+      </c>
+      <c r="C248" s="9">
+        <v>24.0</v>
+      </c>
+      <c r="D248" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E248" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F248" s="9">
+        <v>18.0</v>
+      </c>
+      <c r="G248" s="9">
+        <v>69.0</v>
+      </c>
+      <c r="H248" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B249" s="9">
+        <v>74.0</v>
+      </c>
+      <c r="C249" s="9">
+        <v>22.0</v>
+      </c>
+      <c r="D249" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E249" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F249" s="9">
+        <v>10.0</v>
+      </c>
+      <c r="G249" s="9">
+        <v>86.0</v>
+      </c>
+      <c r="H249" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B250" s="9">
+        <v>69.0</v>
+      </c>
+      <c r="C250" s="9">
+        <v>24.0</v>
+      </c>
+      <c r="D250" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="E250" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F250" s="9">
+        <v>18.0</v>
+      </c>
+      <c r="G250" s="9">
+        <v>68.0</v>
+      </c>
+      <c r="H250" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B251" s="9">
+        <v>96.0</v>
+      </c>
+      <c r="C251" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="D251" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E251" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F251" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="G251" s="9">
+        <v>80.0</v>
+      </c>
+      <c r="H251" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B252" s="9">
+        <v>98.0</v>
+      </c>
+      <c r="C252" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="D252" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E252" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F252" s="9">
+        <v>14.0</v>
+      </c>
+      <c r="G252" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="H252" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B253" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="C253" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="D253" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E253" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F253" s="9">
+        <v>40.0</v>
+      </c>
+      <c r="G253" s="9">
+        <v>80.0</v>
+      </c>
+      <c r="H253" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B254" s="9">
+        <v>5.0</v>
+      </c>
+      <c r="C254" s="9">
+        <v>33.0</v>
+      </c>
+      <c r="D254" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E254" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F254" s="9">
+        <v>75.0</v>
+      </c>
+      <c r="G254" s="9">
+        <v>65.0</v>
+      </c>
+      <c r="H254" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B255" s="9">
+        <v>97.0</v>
+      </c>
+      <c r="C255" s="9">
+        <v>24.0</v>
+      </c>
+      <c r="D255" s="9">
+        <v>5.9</v>
+      </c>
+      <c r="E255" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F255" s="9">
+        <v>15.0</v>
+      </c>
+      <c r="G255" s="9">
+        <v>83.0</v>
+      </c>
+      <c r="H255" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B256" s="9">
+        <v>98.0</v>
+      </c>
+      <c r="C256" s="9">
+        <v>29.0</v>
+      </c>
+      <c r="D256" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="E256" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F256" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="G256" s="9">
+        <v>65.0</v>
+      </c>
+      <c r="H256" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B257" s="9">
+        <v>44.0</v>
+      </c>
+      <c r="C257" s="9">
+        <v>23.0</v>
+      </c>
+      <c r="D257" s="9">
+        <v>7.1</v>
+      </c>
+      <c r="E257" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F257" s="9">
+        <v>40.0</v>
+      </c>
+      <c r="G257" s="9">
+        <v>88.0</v>
+      </c>
+      <c r="H257" s="9">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B258" s="9">
+        <v>43.0</v>
+      </c>
+      <c r="C258" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="D258" s="9">
+        <v>7.3</v>
+      </c>
+      <c r="E258" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F258" s="9">
+        <v>55.0</v>
+      </c>
+      <c r="G258" s="9">
+        <v>80.0</v>
+      </c>
+      <c r="H258" s="9">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B259" s="9">
+        <v>85.0</v>
+      </c>
+      <c r="C259" s="9">
+        <v>20.0</v>
+      </c>
+      <c r="D259" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E259" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F259" s="9">
+        <v>12.0</v>
+      </c>
+      <c r="G259" s="9">
+        <v>84.0</v>
+      </c>
+      <c r="H259" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B260" s="9">
+        <v>78.0</v>
+      </c>
+      <c r="C260" s="9">
+        <v>27.0</v>
+      </c>
+      <c r="D260" s="9">
+        <v>7.1</v>
+      </c>
+      <c r="E260" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F260" s="9">
+        <v>20.0</v>
+      </c>
+      <c r="G260" s="9">
+        <v>68.0</v>
+      </c>
+      <c r="H260" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B261" s="9">
+        <v>80.0</v>
+      </c>
+      <c r="C261" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="D261" s="9">
+        <v>6.9</v>
+      </c>
+      <c r="E261" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F261" s="9">
+        <v>50.0</v>
+      </c>
+      <c r="G261" s="9">
+        <v>36.0</v>
+      </c>
+      <c r="H261" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B262" s="9">
+        <v>70.0</v>
+      </c>
+      <c r="C262" s="9">
+        <v>20.0</v>
+      </c>
+      <c r="D262" s="9">
+        <v>6.7</v>
+      </c>
+      <c r="E262" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F262" s="9">
+        <v>12.0</v>
+      </c>
+      <c r="G262" s="9">
+        <v>83.0</v>
+      </c>
+      <c r="H262" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B263" s="9">
+        <v>63.0</v>
+      </c>
+      <c r="C263" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="D263" s="9">
+        <v>7.1</v>
+      </c>
+      <c r="E263" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F263" s="9">
+        <v>22.0</v>
+      </c>
+      <c r="G263" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="H263" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B264" s="9">
+        <v>74.0</v>
+      </c>
+      <c r="C264" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="D264" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E264" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F264" s="9">
+        <v>50.0</v>
+      </c>
+      <c r="G264" s="9">
+        <v>40.0</v>
+      </c>
+      <c r="H264" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B265" s="9">
+        <v>76.0</v>
+      </c>
+      <c r="C265" s="9">
+        <v>20.0</v>
+      </c>
+      <c r="D265" s="9">
+        <v>6.6</v>
+      </c>
+      <c r="E265" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F265" s="9">
+        <v>12.0</v>
+      </c>
+      <c r="G265" s="9">
+        <v>85.0</v>
+      </c>
+      <c r="H265" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B266" s="9">
+        <v>72.0</v>
+      </c>
+      <c r="C266" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="D266" s="9">
+        <v>6.9</v>
+      </c>
+      <c r="E266" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F266" s="9">
+        <v>22.0</v>
+      </c>
+      <c r="G266" s="9">
+        <v>62.0</v>
+      </c>
+      <c r="H266" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B267" s="9">
+        <v>75.0</v>
+      </c>
+      <c r="C267" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="D267" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E267" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F267" s="9">
+        <v>50.0</v>
+      </c>
+      <c r="G267" s="9">
+        <v>35.0</v>
+      </c>
+      <c r="H267" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B268" s="9">
+        <v>99.0</v>
+      </c>
+      <c r="C268" s="9">
+        <v>22.0</v>
+      </c>
+      <c r="D268" s="9">
+        <v>6.7</v>
+      </c>
+      <c r="E268" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F268" s="9">
+        <v>10.0</v>
+      </c>
+      <c r="G268" s="9">
+        <v>78.0</v>
+      </c>
+      <c r="H268" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B269" s="9">
+        <v>97.0</v>
+      </c>
+      <c r="C269" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="D269" s="9">
+        <v>7.1</v>
+      </c>
+      <c r="E269" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F269" s="9">
+        <v>22.0</v>
+      </c>
+      <c r="G269" s="9">
+        <v>48.0</v>
+      </c>
+      <c r="H269" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B270" s="9">
+        <v>95.0</v>
+      </c>
+      <c r="C270" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="D270" s="9">
+        <v>7.3</v>
+      </c>
+      <c r="E270" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F270" s="9">
+        <v>22.0</v>
+      </c>
+      <c r="G270" s="9">
+        <v>50.0</v>
+      </c>
+      <c r="H270" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B271" s="9">
+        <v>10.0</v>
+      </c>
+      <c r="C271" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="D271" s="9">
+        <v>6.7</v>
+      </c>
+      <c r="E271" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F271" s="9">
+        <v>45.0</v>
+      </c>
+      <c r="G271" s="9">
+        <v>78.0</v>
+      </c>
+      <c r="H271" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B272" s="9">
+        <v>3.0</v>
+      </c>
+      <c r="C272" s="9">
+        <v>34.0</v>
+      </c>
+      <c r="D272" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E272" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F272" s="9">
+        <v>80.0</v>
+      </c>
+      <c r="G272" s="9">
+        <v>62.0</v>
+      </c>
+      <c r="H272" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B273" s="9">
+        <v>9.0</v>
+      </c>
+      <c r="C273" s="9">
+        <v>52.0</v>
+      </c>
+      <c r="D273" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E273" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F273" s="9">
+        <v>200.0</v>
+      </c>
+      <c r="G273" s="9">
+        <v>58.0</v>
+      </c>
+      <c r="H273" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B274" s="9">
+        <v>99.0</v>
+      </c>
+      <c r="C274" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="D274" s="9">
+        <v>6.1</v>
+      </c>
+      <c r="E274" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F274" s="9">
+        <v>18.0</v>
+      </c>
+      <c r="G274" s="9">
+        <v>81.0</v>
+      </c>
+      <c r="H274" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B275" s="9">
+        <v>96.0</v>
+      </c>
+      <c r="C275" s="9">
+        <v>31.0</v>
+      </c>
+      <c r="D275" s="9">
+        <v>6.7</v>
+      </c>
+      <c r="E275" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F275" s="9">
+        <v>32.0</v>
+      </c>
+      <c r="G275" s="9">
+        <v>63.0</v>
+      </c>
+      <c r="H275" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B276" s="9">
+        <v>98.0</v>
+      </c>
+      <c r="C276" s="9">
+        <v>36.0</v>
+      </c>
+      <c r="D276" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E276" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F276" s="9">
+        <v>45.0</v>
+      </c>
+      <c r="G276" s="9">
+        <v>52.0</v>
+      </c>
+      <c r="H276" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B277" s="9">
+        <v>45.0</v>
+      </c>
+      <c r="C277" s="9">
+        <v>22.0</v>
+      </c>
+      <c r="D277" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E277" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F277" s="9">
+        <v>45.0</v>
+      </c>
+      <c r="G277" s="9">
+        <v>86.0</v>
+      </c>
+      <c r="H277" s="9">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B278" s="9">
+        <v>42.0</v>
+      </c>
+      <c r="C278" s="9">
+        <v>27.0</v>
+      </c>
+      <c r="D278" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E278" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F278" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="G278" s="9">
+        <v>78.0</v>
+      </c>
+      <c r="H278" s="9">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B279" s="9">
+        <v>81.0</v>
+      </c>
+      <c r="C279" s="9">
+        <v>24.0</v>
+      </c>
+      <c r="D279" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E279" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F279" s="9">
+        <v>14.0</v>
+      </c>
+      <c r="G279" s="9">
+        <v>82.0</v>
+      </c>
+      <c r="H279" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B280" s="9">
+        <v>79.0</v>
+      </c>
+      <c r="C280" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="D280" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E280" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F280" s="9">
+        <v>22.0</v>
+      </c>
+      <c r="G280" s="9">
+        <v>64.0</v>
+      </c>
+      <c r="H280" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B281" s="9">
+        <v>68.0</v>
+      </c>
+      <c r="C281" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="D281" s="9">
+        <v>6.6</v>
+      </c>
+      <c r="E281" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F281" s="9">
+        <v>14.0</v>
+      </c>
+      <c r="G281" s="9">
+        <v>81.0</v>
+      </c>
+      <c r="H281" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B282" s="9">
+        <v>65.0</v>
+      </c>
+      <c r="C282" s="9">
+        <v>27.0</v>
+      </c>
+      <c r="D282" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E282" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F282" s="9">
+        <v>24.0</v>
+      </c>
+      <c r="G282" s="9">
+        <v>58.0</v>
+      </c>
+      <c r="H282" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B283" s="9">
+        <v>78.0</v>
+      </c>
+      <c r="C283" s="9">
+        <v>24.0</v>
+      </c>
+      <c r="D283" s="9">
+        <v>6.9</v>
+      </c>
+      <c r="E283" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F283" s="9">
+        <v>14.0</v>
+      </c>
+      <c r="G283" s="9">
+        <v>83.0</v>
+      </c>
+      <c r="H283" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B284" s="9">
+        <v>68.0</v>
+      </c>
+      <c r="C284" s="9">
+        <v>27.0</v>
+      </c>
+      <c r="D284" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E284" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F284" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="G284" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="H284" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B285" s="9">
+        <v>98.0</v>
+      </c>
+      <c r="C285" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="D285" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E285" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F285" s="9">
+        <v>12.0</v>
+      </c>
+      <c r="G285" s="9">
+        <v>76.0</v>
+      </c>
+      <c r="H285" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B286" s="9">
+        <v>96.0</v>
+      </c>
+      <c r="C286" s="9">
+        <v>32.0</v>
+      </c>
+      <c r="D286" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E286" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F286" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="G286" s="9">
+        <v>46.0</v>
+      </c>
+      <c r="H286" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B287" s="9">
+        <v>2.0</v>
+      </c>
+      <c r="C287" s="9">
+        <v>29.0</v>
+      </c>
+      <c r="D287" s="9">
+        <v>6.9</v>
+      </c>
+      <c r="E287" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F287" s="9">
+        <v>50.0</v>
+      </c>
+      <c r="G287" s="9">
+        <v>75.0</v>
+      </c>
+      <c r="H287" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B288" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="C288" s="9">
+        <v>36.0</v>
+      </c>
+      <c r="D288" s="9">
+        <v>7.1</v>
+      </c>
+      <c r="E288" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F288" s="9">
+        <v>85.0</v>
+      </c>
+      <c r="G288" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="H288" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B289" s="9">
+        <v>97.0</v>
+      </c>
+      <c r="C289" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="D289" s="9">
+        <v>6.2</v>
+      </c>
+      <c r="E289" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F289" s="9">
+        <v>20.0</v>
+      </c>
+      <c r="G289" s="9">
+        <v>79.0</v>
+      </c>
+      <c r="H289" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B290" s="9">
+        <v>99.0</v>
+      </c>
+      <c r="C290" s="9">
+        <v>33.0</v>
+      </c>
+      <c r="D290" s="9">
+        <v>6.6</v>
+      </c>
+      <c r="E290" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F290" s="9">
+        <v>35.0</v>
+      </c>
+      <c r="G290" s="9">
+        <v>61.0</v>
+      </c>
+      <c r="H290" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B291" s="9">
+        <v>44.0</v>
+      </c>
+      <c r="C291" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="D291" s="9">
+        <v>7.1</v>
+      </c>
+      <c r="E291" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F291" s="9">
+        <v>50.0</v>
+      </c>
+      <c r="G291" s="9">
+        <v>84.0</v>
+      </c>
+      <c r="H291" s="9">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B292" s="9">
+        <v>43.0</v>
+      </c>
+      <c r="C292" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="D292" s="9">
+        <v>6.7</v>
+      </c>
+      <c r="E292" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F292" s="9">
+        <v>65.0</v>
+      </c>
+      <c r="G292" s="9">
+        <v>76.0</v>
+      </c>
+      <c r="H292" s="9">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B293" s="9">
+        <v>83.0</v>
+      </c>
+      <c r="C293" s="9">
+        <v>22.0</v>
+      </c>
+      <c r="D293" s="9">
+        <v>6.9</v>
+      </c>
+      <c r="E293" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F293" s="9">
+        <v>16.0</v>
+      </c>
+      <c r="G293" s="9">
+        <v>80.0</v>
+      </c>
+      <c r="H293" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B294" s="9">
+        <v>76.0</v>
+      </c>
+      <c r="C294" s="9">
+        <v>29.0</v>
+      </c>
+      <c r="D294" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E294" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F294" s="9">
+        <v>24.0</v>
+      </c>
+      <c r="G294" s="9">
+        <v>62.0</v>
+      </c>
+      <c r="H294" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B295" s="9">
+        <v>72.0</v>
+      </c>
+      <c r="C295" s="9">
+        <v>23.0</v>
+      </c>
+      <c r="D295" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E295" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F295" s="9">
+        <v>16.0</v>
+      </c>
+      <c r="G295" s="9">
+        <v>79.0</v>
+      </c>
+      <c r="H295" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B296" s="9">
+        <v>69.0</v>
+      </c>
+      <c r="C296" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="D296" s="9">
+        <v>7.1</v>
+      </c>
+      <c r="E296" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F296" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="G296" s="9">
+        <v>56.0</v>
+      </c>
+      <c r="H296" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B297" s="9">
+        <v>73.0</v>
+      </c>
+      <c r="C297" s="9">
+        <v>25.0</v>
+      </c>
+      <c r="D297" s="9">
+        <v>6.7</v>
+      </c>
+      <c r="E297" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F297" s="9">
+        <v>16.0</v>
+      </c>
+      <c r="G297" s="9">
+        <v>81.0</v>
+      </c>
+      <c r="H297" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B298" s="9">
+        <v>66.0</v>
+      </c>
+      <c r="C298" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="D298" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E298" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F298" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="G298" s="9">
+        <v>58.0</v>
+      </c>
+      <c r="H298" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B299" s="9">
+        <v>99.0</v>
+      </c>
+      <c r="C299" s="9">
+        <v>27.0</v>
+      </c>
+      <c r="D299" s="9">
+        <v>6.9</v>
+      </c>
+      <c r="E299" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F299" s="9">
+        <v>14.0</v>
+      </c>
+      <c r="G299" s="9">
+        <v>74.0</v>
+      </c>
+      <c r="H299" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B300" s="9">
+        <v>95.0</v>
+      </c>
+      <c r="C300" s="9">
+        <v>33.0</v>
+      </c>
+      <c r="D300" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E300" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F300" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="G300" s="9">
+        <v>44.0</v>
+      </c>
+      <c r="H300" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B301" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="C301" s="9">
+        <v>31.0</v>
+      </c>
+      <c r="D301" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E301" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F301" s="9">
+        <v>55.0</v>
+      </c>
+      <c r="G301" s="9">
+        <v>72.0</v>
+      </c>
+      <c r="H301" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B302" s="9">
+        <v>4.0</v>
+      </c>
+      <c r="C302" s="9">
+        <v>38.0</v>
+      </c>
+      <c r="D302" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E302" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F302" s="9">
+        <v>95.0</v>
+      </c>
+      <c r="G302" s="9">
+        <v>57.0</v>
+      </c>
+      <c r="H302" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B303" s="9">
+        <v>98.0</v>
+      </c>
+      <c r="C303" s="9">
+        <v>30.0</v>
+      </c>
+      <c r="D303" s="9">
+        <v>6.3</v>
+      </c>
+      <c r="E303" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F303" s="9">
+        <v>22.0</v>
+      </c>
+      <c r="G303" s="9">
+        <v>77.0</v>
+      </c>
+      <c r="H303" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B304" s="9">
+        <v>95.0</v>
+      </c>
+      <c r="C304" s="9">
+        <v>35.0</v>
+      </c>
+      <c r="D304" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E304" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F304" s="9">
+        <v>38.0</v>
+      </c>
+      <c r="G304" s="9">
+        <v>59.0</v>
+      </c>
+      <c r="H304" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B305" s="9">
+        <v>43.0</v>
+      </c>
+      <c r="C305" s="9">
+        <v>24.0</v>
+      </c>
+      <c r="D305" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="E305" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F305" s="9">
+        <v>55.0</v>
+      </c>
+      <c r="G305" s="9">
+        <v>82.0</v>
+      </c>
+      <c r="H305" s="9">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B306" s="9">
+        <v>45.0</v>
+      </c>
+      <c r="C306" s="9">
+        <v>29.0</v>
+      </c>
+      <c r="D306" s="9">
+        <v>6.9</v>
+      </c>
+      <c r="E306" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F306" s="9">
+        <v>70.0</v>
+      </c>
+      <c r="G306" s="9">
+        <v>74.0</v>
+      </c>
+      <c r="H306" s="9">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B307" s="9">
+        <v>82.0</v>
+      </c>
+      <c r="C307" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="D307" s="9">
+        <v>6.7</v>
+      </c>
+      <c r="E307" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F307" s="9">
+        <v>18.0</v>
+      </c>
+      <c r="G307" s="9">
+        <v>78.0</v>
+      </c>
+      <c r="H307" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B308" s="9">
+        <v>71.0</v>
+      </c>
+      <c r="C308" s="9">
+        <v>20.0</v>
+      </c>
+      <c r="D308" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="E308" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F308" s="9">
+        <v>18.0</v>
+      </c>
+      <c r="G308" s="9">
+        <v>77.0</v>
+      </c>
+      <c r="H308" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B309" s="9">
+        <v>70.0</v>
+      </c>
+      <c r="C309" s="9">
+        <v>28.0</v>
+      </c>
+      <c r="D309" s="9">
+        <v>6.6</v>
+      </c>
+      <c r="E309" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F309" s="9">
+        <v>18.0</v>
+      </c>
+      <c r="G309" s="9">
+        <v>79.0</v>
+      </c>
+      <c r="H309" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B310" s="9">
+        <v>97.0</v>
+      </c>
+      <c r="C310" s="9">
+        <v>23.0</v>
+      </c>
+      <c r="D310" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="E310" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F310" s="9">
+        <v>16.0</v>
+      </c>
+      <c r="G310" s="9">
+        <v>72.0</v>
+      </c>
+      <c r="H310" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B311" s="9">
+        <v>6.0</v>
+      </c>
+      <c r="C311" s="9">
+        <v>40.0</v>
+      </c>
+      <c r="D311" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="E311" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F311" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="G311" s="9">
+        <v>70.0</v>
+      </c>
+      <c r="H311" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B312" s="9">
+        <v>99.0</v>
+      </c>
+      <c r="C312" s="9">
+        <v>38.0</v>
+      </c>
+      <c r="D312" s="9">
+        <v>6.4</v>
+      </c>
+      <c r="E312" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F312" s="9">
+        <v>50.0</v>
+      </c>
+      <c r="G312" s="9">
+        <v>50.0</v>
+      </c>
+      <c r="H312" s="9">
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
